--- a/data/snapshots/ca.xlsx
+++ b/data/snapshots/ca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29AF7EE8-79B1-4F51-BE6A-4B705A337962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE79D4D-0B77-47F4-A288-FAD4FDF0655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -15363,14 +15363,14 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEAC05D-976A-4D1B-BF88-C07869576FC8}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>

--- a/data/snapshots/ca.xlsx
+++ b/data/snapshots/ca.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFE79D4D-0B77-47F4-A288-FAD4FDF0655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66561CC6-3A32-444D-BAF5-6F490CB904D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="771">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2339,6 +2339,81 @@
     <t>1520 E. Sepulveda Blvd.  Carson CA 90745</t>
   </si>
   <si>
+    <t>5820 Owens Dr.  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>The Neil Jones Food Company dba Tomatek</t>
+  </si>
+  <si>
+    <t>2025 N Street  Firebaugh CA 93622</t>
+  </si>
+  <si>
+    <t>Menzies Aviation</t>
+  </si>
+  <si>
+    <t>1 World Way  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Fender Musical Instruments Corporation</t>
+  </si>
+  <si>
+    <t>311 Cessna Circle  Corona CA 92878</t>
+  </si>
+  <si>
+    <t>Myers Power Products, Inc.</t>
+  </si>
+  <si>
+    <t>2950 East Philadelphia Street  Ontario CA 91761</t>
+  </si>
+  <si>
+    <t>Formagrid Inc. dba Airtable</t>
+  </si>
+  <si>
+    <t>One Front Street, 28th Floor  San Francisco CA 94111</t>
+  </si>
+  <si>
+    <t>Silverado Senior Living Managment Inc.</t>
+  </si>
+  <si>
+    <t>514 North Prospect Avenue  Redondo Beach CA 90277</t>
+  </si>
+  <si>
+    <t>Baloian Farms</t>
+  </si>
+  <si>
+    <t>446 N. Blythe Ave.  Fresno CA 93706</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (1800 Harrison St.)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (One Kaiser Plaza)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (75 N. Fair Oaks Ave.)</t>
+  </si>
+  <si>
+    <t>Kaiser Foundation Hospitals and Kaiser Foundation Health Plan, Inc. (99 S. Oakland Ave.)</t>
+  </si>
+  <si>
+    <t>1650 Los Gamos Dr.  San Rafael CA 94903</t>
+  </si>
+  <si>
+    <t>Tree Service Unlimited Inc.</t>
+  </si>
+  <si>
+    <t>4080 Plaza Goldorado Circle Ste A  Cameron Park CA 95682</t>
+  </si>
+  <si>
+    <t>5808 Sunset Blvd  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>121 Albright Way  Los Gatos CA 95032</t>
+  </si>
+  <si>
+    <t>Relocation Permanent</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2358,7 +2433,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/14/2026
+01/01/2023 - 10/21/2026
 </t>
     </r>
     <r>
@@ -2372,19 +2447,25 @@
     </r>
   </si>
   <si>
-    <t>5820 Owens Dr.  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>The Neil Jones Food Company dba Tomatek</t>
-  </si>
-  <si>
-    <t>2025 N Street  Firebaugh CA 93622</t>
-  </si>
-  <si>
-    <t>Menzies Aviation</t>
-  </si>
-  <si>
-    <t>1 World Way  Los Angeles CA 90045</t>
+    <t>Safeway, Inc.</t>
+  </si>
+  <si>
+    <t>905 South 34th Street  Richmond CA 94804</t>
+  </si>
+  <si>
+    <t>Randstad (Dreyer's Grand Ice Cream)</t>
+  </si>
+  <si>
+    <t>eBay Inc.</t>
+  </si>
+  <si>
+    <t>2025 Hamilton Ave  San Jose CA 95125</t>
+  </si>
+  <si>
+    <t>4941 Allison Parkway Suite B Vacaville CA 95688</t>
+  </si>
+  <si>
+    <t>970 E Continental  Tulare CA 93274</t>
   </si>
   <si>
     <r>
@@ -2398,7 +2479,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/14/2026</t>
+      <t>07/01/26 to 10/21/2026</t>
     </r>
     <r>
       <rPr>
@@ -2418,7 +2499,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I370.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I392.</t>
     </r>
   </si>
 </sst>
@@ -3224,6 +3305,42 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3488,42 +3605,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E7"/>
@@ -3586,35 +3667,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}" name="WarnReportSummary" displayName="WarnReportSummary" ref="A2:B9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A2:B9" xr:uid="{BE651B3D-87EE-436C-B33F-C1564840D30D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{27E39F38-3125-453D-8079-314461C0A408}" name="Report Summary" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{BC59C82C-A192-4C58-973D-25AB492E21BC}" name="Total" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I370" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A2:I370" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I392" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I392" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I358">
     <sortCondition ref="C2:C358"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{C6D12265-C94C-4E06-8034-3C717447E155}" name="Processed_x000a_Date" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{B3ED9634-5328-42A8-B322-3BC02B1B09B6}" name="Effective _x000a_Date" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{9D38EF5A-DEC2-4452-98D6-CF4FB3342379}" name="Company" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{211DDDC0-B68A-4CB6-AB53-3FF3E63F26A0}" name="Layoff/_x000a_Closure" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{5A996A7E-F604-41CE-AC0B-D6BC2FB09F5A}" name="No. Of_x000a_Employees" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{6BB24B8B-7A22-4DE0-B907-BC4F68AE8678}" name="Address" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{695F1FD1-01CF-43F8-8B40-37D320A0AC01}" name="Related Industry" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4022,7 +4103,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>17617</v>
+        <v>21262</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4031,7 +4112,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4040,7 +4121,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4058,7 +4139,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4067,7 +4148,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,7 +4171,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I370"/>
+  <dimension ref="A1:I392"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4106,7 +4187,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -8158,7 +8239,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>6</v>
+        <v>761</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -14660,7 +14741,7 @@
         <v>7</v>
       </c>
       <c r="H365" s="30" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I365" s="31" t="s">
         <v>45</v>
@@ -14767,7 +14848,7 @@
         <v>46370</v>
       </c>
       <c r="E369" s="28" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F369" s="28" t="s">
         <v>129</v>
@@ -14776,7 +14857,7 @@
         <v>116</v>
       </c>
       <c r="H369" s="30" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="I369" s="31" t="s">
         <v>34</v>
@@ -14796,7 +14877,7 @@
         <v>46345</v>
       </c>
       <c r="E370" s="28" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="F370" s="28" t="s">
         <v>6</v>
@@ -14805,10 +14886,648 @@
         <v>137</v>
       </c>
       <c r="H370" s="30" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I370" s="31" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B371" s="29">
+        <v>46310</v>
+      </c>
+      <c r="C371" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D371" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E371" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="F371" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G371" s="30">
+        <v>533</v>
+      </c>
+      <c r="H371" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="I371" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B372" s="29">
+        <v>46304</v>
+      </c>
+      <c r="C372" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D372" s="29">
+        <v>46371</v>
+      </c>
+      <c r="E372" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="F372" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G372" s="30">
+        <v>206</v>
+      </c>
+      <c r="H372" s="30" t="s">
+        <v>745</v>
+      </c>
+      <c r="I372" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B373" s="29">
+        <v>46310</v>
+      </c>
+      <c r="C373" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D373" s="29">
+        <v>46402</v>
+      </c>
+      <c r="E373" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="F373" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G373" s="30">
+        <v>190</v>
+      </c>
+      <c r="H373" s="30" t="s">
+        <v>747</v>
+      </c>
+      <c r="I373" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B374" s="29">
+        <v>46309</v>
+      </c>
+      <c r="C374" s="29">
+        <v>46310</v>
+      </c>
+      <c r="D374" s="29">
+        <v>46371</v>
+      </c>
+      <c r="E374" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="F374" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G374" s="30">
+        <v>7</v>
+      </c>
+      <c r="H374" s="30" t="s">
+        <v>749</v>
+      </c>
+      <c r="I374" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="B375" s="29">
+        <v>46296</v>
+      </c>
+      <c r="C375" s="29">
+        <v>46311</v>
+      </c>
+      <c r="D375" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E375" s="28" t="s">
+        <v>750</v>
+      </c>
+      <c r="F375" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G375" s="30">
+        <v>106</v>
+      </c>
+      <c r="H375" s="30" t="s">
+        <v>751</v>
+      </c>
+      <c r="I375" s="31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B376" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C376" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D376" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E376" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="F376" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G376" s="30">
+        <v>1</v>
+      </c>
+      <c r="H376" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="I376" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B377" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C377" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D377" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E377" s="28" t="s">
+        <v>753</v>
+      </c>
+      <c r="F377" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G377" s="30">
+        <v>5</v>
+      </c>
+      <c r="H377" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="I377" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B378" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C378" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D378" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E378" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="F378" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G378" s="30">
+        <v>1</v>
+      </c>
+      <c r="H378" s="30" t="s">
+        <v>588</v>
+      </c>
+      <c r="I378" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B379" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C379" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D379" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E379" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="F379" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G379" s="30">
+        <v>1</v>
+      </c>
+      <c r="H379" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="I379" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="28" t="s">
+        <v>634</v>
+      </c>
+      <c r="B380" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C380" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D380" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E380" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F380" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G380" s="30">
+        <v>1</v>
+      </c>
+      <c r="H380" s="30" t="s">
+        <v>756</v>
+      </c>
+      <c r="I380" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B381" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C381" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D381" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E381" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F381" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G381" s="30">
+        <v>1</v>
+      </c>
+      <c r="H381" s="30" t="s">
+        <v>595</v>
+      </c>
+      <c r="I381" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B382" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C382" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D382" s="29">
+        <v>46374</v>
+      </c>
+      <c r="E382" s="28" t="s">
+        <v>715</v>
+      </c>
+      <c r="F382" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G382" s="30">
+        <v>1</v>
+      </c>
+      <c r="H382" s="30" t="s">
+        <v>596</v>
+      </c>
+      <c r="I382" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="B383" s="29">
+        <v>46308</v>
+      </c>
+      <c r="C383" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D383" s="29">
+        <v>46370</v>
+      </c>
+      <c r="E383" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="F383" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G383" s="30">
+        <v>137</v>
+      </c>
+      <c r="H383" s="30" t="s">
+        <v>758</v>
+      </c>
+      <c r="I383" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B384" s="29">
+        <v>46311</v>
+      </c>
+      <c r="C384" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D384" s="29">
+        <v>46279</v>
+      </c>
+      <c r="E384" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F384" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G384" s="30">
+        <v>267</v>
+      </c>
+      <c r="H384" s="30" t="s">
+        <v>759</v>
+      </c>
+      <c r="I384" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B385" s="29">
+        <v>46311</v>
+      </c>
+      <c r="C385" s="29">
+        <v>46314</v>
+      </c>
+      <c r="D385" s="29">
+        <v>46279</v>
+      </c>
+      <c r="E385" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F385" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G385" s="30">
+        <v>227</v>
+      </c>
+      <c r="H385" s="30" t="s">
+        <v>760</v>
+      </c>
+      <c r="I385" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B386" s="29">
+        <v>46315</v>
+      </c>
+      <c r="C386" s="29">
+        <v>46315</v>
+      </c>
+      <c r="D386" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E386" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F386" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G386" s="30">
+        <v>380</v>
+      </c>
+      <c r="H386" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="I386" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B387" s="29">
+        <v>46315</v>
+      </c>
+      <c r="C387" s="29">
+        <v>46315</v>
+      </c>
+      <c r="D387" s="29">
+        <v>46376</v>
+      </c>
+      <c r="E387" s="28" t="s">
+        <v>763</v>
+      </c>
+      <c r="F387" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G387" s="30">
+        <v>92</v>
+      </c>
+      <c r="H387" s="30" t="s">
+        <v>764</v>
+      </c>
+      <c r="I387" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B388" s="29">
+        <v>46315</v>
+      </c>
+      <c r="C388" s="29">
+        <v>46315</v>
+      </c>
+      <c r="D388" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E388" s="28" t="s">
+        <v>765</v>
+      </c>
+      <c r="F388" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G388" s="30">
+        <v>91</v>
+      </c>
+      <c r="H388" s="30" t="s">
+        <v>627</v>
+      </c>
+      <c r="I388" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B389" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C389" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D389" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E389" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F389" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G389" s="30">
+        <v>715</v>
+      </c>
+      <c r="H389" s="30" t="s">
+        <v>618</v>
+      </c>
+      <c r="I389" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B390" s="29">
+        <v>46316</v>
+      </c>
+      <c r="C390" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D390" s="29">
+        <v>46316</v>
+      </c>
+      <c r="E390" s="28" t="s">
+        <v>766</v>
+      </c>
+      <c r="F390" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G390" s="30">
+        <v>229</v>
+      </c>
+      <c r="H390" s="30" t="s">
+        <v>767</v>
+      </c>
+      <c r="I390" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B391" s="29">
+        <v>46316</v>
+      </c>
+      <c r="C391" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D391" s="29">
+        <v>46379</v>
+      </c>
+      <c r="E391" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="F391" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G391" s="30">
+        <v>6</v>
+      </c>
+      <c r="H391" s="30" t="s">
+        <v>768</v>
+      </c>
+      <c r="I391" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B392" s="29">
+        <v>46314</v>
+      </c>
+      <c r="C392" s="29">
+        <v>46316</v>
+      </c>
+      <c r="D392" s="29">
+        <v>46375</v>
+      </c>
+      <c r="E392" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="F392" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G392" s="30">
+        <v>448</v>
+      </c>
+      <c r="H392" s="30" t="s">
+        <v>769</v>
+      </c>
+      <c r="I392" s="31" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -14825,7 +15544,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I370</xm:sqref>
+          <xm:sqref>I3:I392</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14946,7 +15665,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="E1"/>
     </row>
@@ -15134,26 +15853,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E614ED5C53901F4C88FF6AEBBF3D8E0D" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="529ed3825ab478a5ffdc44eb265dc6f5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82b749e3-8208-459a-bfc0-9b428d09cbab" xmlns:ns3="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7c2030912f9588e16c624efbe24e62a" ns2:_="" ns3:_="">
     <xsd:import namespace="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
@@ -15360,33 +16059,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CEAC05D-976A-4D1B-BF88-C07869576FC8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50F94E65-68E1-47F0-9BED-AA8CE5F487F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78C5D531-1085-40EB-9017-D3176F92DEED}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177B7A0E-FF32-4156-AD26-40F8A8D9C534}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -15404,8 +16098,33 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F132A3CF-F853-4244-80FB-C7965FFC7437}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B30A08B-9F6D-4095-B44F-A85D48EE2410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/snapshots/ca.xlsx
+++ b/data/snapshots/ca.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66561CC6-3A32-444D-BAF5-6F490CB904D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46201A9A-59F8-4028-AF33-2BE8FF906E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="784">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2414,6 +2414,27 @@
     <t>Relocation Permanent</t>
   </si>
   <si>
+    <t>Safeway, Inc.</t>
+  </si>
+  <si>
+    <t>905 South 34th Street  Richmond CA 94804</t>
+  </si>
+  <si>
+    <t>Randstad (Dreyer's Grand Ice Cream)</t>
+  </si>
+  <si>
+    <t>eBay Inc.</t>
+  </si>
+  <si>
+    <t>2025 Hamilton Ave  San Jose CA 95125</t>
+  </si>
+  <si>
+    <t>4941 Allison Parkway Suite B Vacaville CA 95688</t>
+  </si>
+  <si>
+    <t>970 E Continental  Tulare CA 93274</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2433,7 +2454,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/21/2026
+01/01/2023 - 10/26/2026
 </t>
     </r>
     <r>
@@ -2447,25 +2468,43 @@
     </r>
   </si>
   <si>
-    <t>Safeway, Inc.</t>
-  </si>
-  <si>
-    <t>905 South 34th Street  Richmond CA 94804</t>
-  </si>
-  <si>
-    <t>Randstad (Dreyer's Grand Ice Cream)</t>
-  </si>
-  <si>
-    <t>eBay Inc.</t>
-  </si>
-  <si>
-    <t>2025 Hamilton Ave  San Jose CA 95125</t>
-  </si>
-  <si>
-    <t>4941 Allison Parkway Suite B Vacaville CA 95688</t>
-  </si>
-  <si>
-    <t>970 E Continental  Tulare CA 93274</t>
+    <t>Georg Fischer Signet LLC</t>
+  </si>
+  <si>
+    <t>5462 North Irwindale Avenue  Baldwin Park CA 91706</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>1900 Prairie City Road  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>24Hr Homecare</t>
+  </si>
+  <si>
+    <t>Conduent State &amp; Local Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>375 Beale Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>The Madrona</t>
+  </si>
+  <si>
+    <t>1001 Westside Road  Healdsburg CA 95448</t>
+  </si>
+  <si>
+    <t>Everidge Inc.</t>
+  </si>
+  <si>
+    <t>8886 White Oak Ave  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Tawa, Inc. dba 99 Ranch Market</t>
+  </si>
+  <si>
+    <t>4024 Grand Avenue  Chino CA 91710</t>
   </si>
   <si>
     <r>
@@ -2479,7 +2518,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/21/2026</t>
+      <t>07/01/26 to 10/26/2026</t>
     </r>
     <r>
       <rPr>
@@ -2499,7 +2538,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I392.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I399.</t>
     </r>
   </si>
 </sst>
@@ -3681,10 +3720,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I392" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I392" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I358">
-    <sortCondition ref="C2:C358"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I399" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I399" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I399">
+    <sortCondition ref="C2:C399"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
@@ -4103,7 +4142,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>21262</v>
+        <v>22591</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4112,7 +4151,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4139,7 +4178,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4148,7 +4187,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4171,7 +4210,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I392"/>
+  <dimension ref="A1:I399"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4187,7 +4226,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>770</v>
+        <v>783</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -14590,7 +14629,7 @@
         <v>338</v>
       </c>
       <c r="F360" s="38" t="s">
-        <v>6</v>
+        <v>761</v>
       </c>
       <c r="G360" s="39">
         <v>74</v>
@@ -15370,7 +15409,7 @@
         <v>46376</v>
       </c>
       <c r="E387" s="28" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F387" s="28" t="s">
         <v>52</v>
@@ -15379,7 +15418,7 @@
         <v>92</v>
       </c>
       <c r="H387" s="30" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="I387" s="31" t="s">
         <v>36</v>
@@ -15399,7 +15438,7 @@
         <v>46375</v>
       </c>
       <c r="E388" s="28" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F388" s="28" t="s">
         <v>101</v>
@@ -15457,7 +15496,7 @@
         <v>46316</v>
       </c>
       <c r="E390" s="28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F390" s="28" t="s">
         <v>6</v>
@@ -15466,7 +15505,7 @@
         <v>229</v>
       </c>
       <c r="H390" s="30" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="I390" s="31" t="s">
         <v>36</v>
@@ -15495,7 +15534,7 @@
         <v>6</v>
       </c>
       <c r="H391" s="30" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I391" s="31" t="s">
         <v>34</v>
@@ -15524,10 +15563,213 @@
         <v>448</v>
       </c>
       <c r="H392" s="30" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I392" s="31" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B393" s="29">
+        <v>46317</v>
+      </c>
+      <c r="C393" s="29">
+        <v>46317</v>
+      </c>
+      <c r="D393" s="29">
+        <v>46377</v>
+      </c>
+      <c r="E393" s="28" t="s">
+        <v>770</v>
+      </c>
+      <c r="F393" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G393" s="30">
+        <v>107</v>
+      </c>
+      <c r="H393" s="30" t="s">
+        <v>771</v>
+      </c>
+      <c r="I393" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B394" s="29">
+        <v>46317</v>
+      </c>
+      <c r="C394" s="29">
+        <v>46317</v>
+      </c>
+      <c r="D394" s="29">
+        <v>46326</v>
+      </c>
+      <c r="E394" s="28" t="s">
+        <v>772</v>
+      </c>
+      <c r="F394" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G394" s="30">
+        <v>67</v>
+      </c>
+      <c r="H394" s="30" t="s">
+        <v>773</v>
+      </c>
+      <c r="I394" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B395" s="29">
+        <v>46296</v>
+      </c>
+      <c r="C395" s="29">
+        <v>46317</v>
+      </c>
+      <c r="D395" s="29">
+        <v>46373</v>
+      </c>
+      <c r="E395" s="28" t="s">
+        <v>774</v>
+      </c>
+      <c r="F395" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G395" s="30">
+        <v>875</v>
+      </c>
+      <c r="H395" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="I395" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B396" s="29">
+        <v>46318</v>
+      </c>
+      <c r="C396" s="29">
+        <v>46318</v>
+      </c>
+      <c r="D396" s="29">
+        <v>46378</v>
+      </c>
+      <c r="E396" s="28" t="s">
+        <v>775</v>
+      </c>
+      <c r="F396" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G396" s="30">
+        <v>64</v>
+      </c>
+      <c r="H396" s="30" t="s">
+        <v>776</v>
+      </c>
+      <c r="I396" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B397" s="29">
+        <v>46318</v>
+      </c>
+      <c r="C397" s="29">
+        <v>46318</v>
+      </c>
+      <c r="D397" s="29">
+        <v>46390</v>
+      </c>
+      <c r="E397" s="28" t="s">
+        <v>777</v>
+      </c>
+      <c r="F397" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G397" s="30">
+        <v>77</v>
+      </c>
+      <c r="H397" s="30" t="s">
+        <v>778</v>
+      </c>
+      <c r="I397" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B398" s="29">
+        <v>46320</v>
+      </c>
+      <c r="C398" s="29">
+        <v>46321</v>
+      </c>
+      <c r="D398" s="29">
+        <v>46444</v>
+      </c>
+      <c r="E398" s="28" t="s">
+        <v>779</v>
+      </c>
+      <c r="F398" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G398" s="30">
+        <v>90</v>
+      </c>
+      <c r="H398" s="30" t="s">
+        <v>780</v>
+      </c>
+      <c r="I398" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B399" s="29">
+        <v>46321</v>
+      </c>
+      <c r="C399" s="29">
+        <v>46321</v>
+      </c>
+      <c r="D399" s="29">
+        <v>46341</v>
+      </c>
+      <c r="E399" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="F399" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G399" s="30">
+        <v>49</v>
+      </c>
+      <c r="H399" s="30" t="s">
+        <v>782</v>
+      </c>
+      <c r="I399" s="31" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -15544,7 +15786,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I392</xm:sqref>
+          <xm:sqref>I3:I399</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15665,7 +15907,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="E1"/>
     </row>
@@ -16080,7 +16322,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{177B7A0E-FF32-4156-AD26-40F8A8D9C534}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06AAF0C6-DE3D-476D-9B1D-F81EEFA6A2CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -16099,7 +16341,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F132A3CF-F853-4244-80FB-C7965FFC7437}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CABCB53B-22C4-40C0-95FE-544F4A875480}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -16107,18 +16349,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B30A08B-9F6D-4095-B44F-A85D48EE2410}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFF7ECC-0EEC-4B7B-ADE7-60BC8E4EAFF1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/snapshots/ca.xlsx
+++ b/data/snapshots/ca.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46201A9A-59F8-4028-AF33-2BE8FF906E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A42485FE-752A-45F7-9928-3A53A1E2F048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="796">
   <si>
     <t>County/Parish</t>
   </si>
@@ -2435,6 +2435,45 @@
     <t>970 E Continental  Tulare CA 93274</t>
   </si>
   <si>
+    <t>Georg Fischer Signet LLC</t>
+  </si>
+  <si>
+    <t>5462 North Irwindale Avenue  Baldwin Park CA 91706</t>
+  </si>
+  <si>
+    <t>Intel Corporation</t>
+  </si>
+  <si>
+    <t>1900 Prairie City Road  Folsom CA 95630</t>
+  </si>
+  <si>
+    <t>24Hr Homecare</t>
+  </si>
+  <si>
+    <t>Conduent State &amp; Local Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>375 Beale Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>The Madrona</t>
+  </si>
+  <si>
+    <t>1001 Westside Road  Healdsburg CA 95448</t>
+  </si>
+  <si>
+    <t>Everidge Inc.</t>
+  </si>
+  <si>
+    <t>8886 White Oak Ave  Rancho Cucamonga CA 91730</t>
+  </si>
+  <si>
+    <t>Tawa, Inc. dba 99 Ranch Market</t>
+  </si>
+  <si>
+    <t>4024 Grand Avenue  Chino CA 91710</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -2454,7 +2493,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 10/26/2026
+01/01/2023 - 10/28/2026
 </t>
     </r>
     <r>
@@ -2468,43 +2507,40 @@
     </r>
   </si>
   <si>
-    <t>Georg Fischer Signet LLC</t>
-  </si>
-  <si>
-    <t>5462 North Irwindale Avenue  Baldwin Park CA 91706</t>
-  </si>
-  <si>
-    <t>Intel Corporation</t>
-  </si>
-  <si>
-    <t>1900 Prairie City Road  Folsom CA 95630</t>
-  </si>
-  <si>
-    <t>24Hr Homecare</t>
-  </si>
-  <si>
-    <t>Conduent State &amp; Local Solutions, Inc.</t>
-  </si>
-  <si>
-    <t>375 Beale Street  San Francisco CA 94105</t>
-  </si>
-  <si>
-    <t>The Madrona</t>
-  </si>
-  <si>
-    <t>1001 Westside Road  Healdsburg CA 95448</t>
-  </si>
-  <si>
-    <t>Everidge Inc.</t>
-  </si>
-  <si>
-    <t>8886 White Oak Ave  Rancho Cucamonga CA 91730</t>
-  </si>
-  <si>
-    <t>Tawa, Inc. dba 99 Ranch Market</t>
-  </si>
-  <si>
-    <t>4024 Grand Avenue  Chino CA 91710</t>
+    <t>4299 Rosewood Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>Frontapp, Inc.</t>
+  </si>
+  <si>
+    <t>One Montgomery Street, Suite 1300  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>Walt Disney Parks &amp; Resorts US, Inc.</t>
+  </si>
+  <si>
+    <t>1401 Flower Street  Glendale CA 91201</t>
+  </si>
+  <si>
+    <t>Levy</t>
+  </si>
+  <si>
+    <t>7000 S Coliseum Way  Oakland CA 94621</t>
+  </si>
+  <si>
+    <t>Artiva Biotherapeutics, Inc.</t>
+  </si>
+  <si>
+    <t>5505 Morehouse Drive, Suite 100  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Dropbox, Inc.</t>
+  </si>
+  <si>
+    <t>50 Hawthorne Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>24 Hr Homecare</t>
   </si>
   <si>
     <r>
@@ -2518,7 +2554,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 10/26/2026</t>
+      <t>07/01/26 to 10/28/2026</t>
     </r>
     <r>
       <rPr>
@@ -2538,7 +2574,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I399.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I406.</t>
     </r>
   </si>
 </sst>
@@ -3720,8 +3756,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I399" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I399" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I406" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I406" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I399">
     <sortCondition ref="C2:C399"/>
   </sortState>
@@ -4142,7 +4178,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>22591</v>
+        <v>23240</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4151,7 +4187,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4178,7 +4214,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4210,7 +4246,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:I406"/>
   <sheetFormatPr defaultColWidth="150.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -4226,7 +4262,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -15583,7 +15619,7 @@
         <v>46377</v>
       </c>
       <c r="E393" s="28" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F393" s="28" t="s">
         <v>101</v>
@@ -15592,7 +15628,7 @@
         <v>107</v>
       </c>
       <c r="H393" s="30" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="I393" s="31" t="s">
         <v>34</v>
@@ -15612,7 +15648,7 @@
         <v>46326</v>
       </c>
       <c r="E394" s="28" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F394" s="28" t="s">
         <v>6</v>
@@ -15621,7 +15657,7 @@
         <v>67</v>
       </c>
       <c r="H394" s="30" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="I394" s="31" t="s">
         <v>34</v>
@@ -15641,7 +15677,7 @@
         <v>46373</v>
       </c>
       <c r="E395" s="28" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="F395" s="28" t="s">
         <v>6</v>
@@ -15670,7 +15706,7 @@
         <v>46378</v>
       </c>
       <c r="E396" s="28" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F396" s="28" t="s">
         <v>6</v>
@@ -15679,7 +15715,7 @@
         <v>64</v>
       </c>
       <c r="H396" s="30" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I396" s="31" t="s">
         <v>41</v>
@@ -15699,7 +15735,7 @@
         <v>46390</v>
       </c>
       <c r="E397" s="28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F397" s="28" t="s">
         <v>101</v>
@@ -15708,7 +15744,7 @@
         <v>77</v>
       </c>
       <c r="H397" s="30" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="I397" s="31" t="s">
         <v>47</v>
@@ -15728,7 +15764,7 @@
         <v>46444</v>
       </c>
       <c r="E398" s="28" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F398" s="28" t="s">
         <v>52</v>
@@ -15737,7 +15773,7 @@
         <v>90</v>
       </c>
       <c r="H398" s="30" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="I398" s="31" t="s">
         <v>34</v>
@@ -15757,7 +15793,7 @@
         <v>46341</v>
       </c>
       <c r="E399" s="28" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F399" s="28" t="s">
         <v>52</v>
@@ -15766,10 +15802,213 @@
         <v>49</v>
       </c>
       <c r="H399" s="30" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I399" s="31" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B400" s="29">
+        <v>46321</v>
+      </c>
+      <c r="C400" s="29">
+        <v>46322</v>
+      </c>
+      <c r="D400" s="29">
+        <v>46361</v>
+      </c>
+      <c r="E400" s="28" t="s">
+        <v>780</v>
+      </c>
+      <c r="F400" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G400" s="30">
+        <v>54</v>
+      </c>
+      <c r="H400" s="30" t="s">
+        <v>783</v>
+      </c>
+      <c r="I400" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B401" s="29">
+        <v>46322</v>
+      </c>
+      <c r="C401" s="29">
+        <v>46322</v>
+      </c>
+      <c r="D401" s="29">
+        <v>46322</v>
+      </c>
+      <c r="E401" s="28" t="s">
+        <v>784</v>
+      </c>
+      <c r="F401" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G401" s="30">
+        <v>53</v>
+      </c>
+      <c r="H401" s="30" t="s">
+        <v>785</v>
+      </c>
+      <c r="I401" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B402" s="29">
+        <v>46322</v>
+      </c>
+      <c r="C402" s="29">
+        <v>46322</v>
+      </c>
+      <c r="D402" s="29">
+        <v>46385</v>
+      </c>
+      <c r="E402" s="28" t="s">
+        <v>786</v>
+      </c>
+      <c r="F402" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G402" s="30">
+        <v>159</v>
+      </c>
+      <c r="H402" s="30" t="s">
+        <v>787</v>
+      </c>
+      <c r="I402" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B403" s="29">
+        <v>46321</v>
+      </c>
+      <c r="C403" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D403" s="29">
+        <v>46387</v>
+      </c>
+      <c r="E403" s="28" t="s">
+        <v>788</v>
+      </c>
+      <c r="F403" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G403" s="30">
+        <v>181</v>
+      </c>
+      <c r="H403" s="30" t="s">
+        <v>789</v>
+      </c>
+      <c r="I403" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B404" s="29">
+        <v>46322</v>
+      </c>
+      <c r="C404" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D404" s="29">
+        <v>46387</v>
+      </c>
+      <c r="E404" s="28" t="s">
+        <v>790</v>
+      </c>
+      <c r="F404" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G404" s="30">
+        <v>131</v>
+      </c>
+      <c r="H404" s="30" t="s">
+        <v>791</v>
+      </c>
+      <c r="I404" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B405" s="29">
+        <v>46323</v>
+      </c>
+      <c r="C405" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D405" s="29">
+        <v>46344</v>
+      </c>
+      <c r="E405" s="28" t="s">
+        <v>792</v>
+      </c>
+      <c r="F405" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G405" s="30">
+        <v>57</v>
+      </c>
+      <c r="H405" s="30" t="s">
+        <v>793</v>
+      </c>
+      <c r="I405" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B406" s="29">
+        <v>46323</v>
+      </c>
+      <c r="C406" s="29">
+        <v>46323</v>
+      </c>
+      <c r="D406" s="29">
+        <v>46388</v>
+      </c>
+      <c r="E406" s="28" t="s">
+        <v>794</v>
+      </c>
+      <c r="F406" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G406" s="30">
+        <v>14</v>
+      </c>
+      <c r="H406" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="I406" s="31" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -15786,7 +16025,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I399</xm:sqref>
+          <xm:sqref>I3:I406</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -15907,7 +16146,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>769</v>
+        <v>782</v>
       </c>
       <c r="E1"/>
     </row>
@@ -16322,7 +16561,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06AAF0C6-DE3D-476D-9B1D-F81EEFA6A2CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87E374AB-C302-426A-962E-8F6AA4A44C39}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -16341,7 +16580,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CABCB53B-22C4-40C0-95FE-544F4A875480}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5906BE0B-8873-41DD-ABB1-29AA0AF4902E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -16349,18 +16588,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FFF7ECC-0EEC-4B7B-ADE7-60BC8E4EAFF1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C4E6149-676B-4118-B2C4-FCABD412CE0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
